--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="64">
   <si>
     <t>Profile</t>
   </si>
@@ -185,19 +185,16 @@
     <t>MII PR SE Kopfumfang</t>
   </si>
   <si>
-    <t>Observation Category Codes#vital-signs, SNOMED CT#248326004, SNOMED CT#null</t>
-  </si>
-  <si>
     <t>null#9843-4, null#null</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>SNOMED CT#69536005</t>
+    <t>dateTime, Period</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
   <si>
     <t>mii-pr-seltene-taillenumfang</t>
@@ -946,19 +943,19 @@
         <v>56</v>
       </c>
       <c r="C18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="D18" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s" s="2">
+      <c r="F18" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="F18" t="s" s="2">
+      <c r="G18" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>60</v>
@@ -967,7 +964,7 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>14</v>
@@ -975,10 +972,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>22</v>
@@ -987,7 +984,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>14</v>
